--- a/reports/pdf_change_20260706.xlsx
+++ b/reports/pdf_change_20260706.xlsx
@@ -172,11 +172,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -568,14 +568,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,341억      당일 2026-07-06  vs  전영업일 2026-07-03      매수 1종목  /  매도 1종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,385억      당일 2026-07-06  vs  전영업일 2026-07-03      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -671,10 +671,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>821214000</v>
+        <v>819666000</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0.154</v>
+        <v>0.152</v>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -690,10 +690,10 @@
         <v>-70</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1075429600</v>
+        <v>-1073402400</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>-0.201</v>
+        <v>-0.199</v>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,858억      당일 2026-07-06  vs  전영업일 2026-07-03      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,769억      당일 2026-07-06  vs  전영업일 2026-07-03      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B8" s="4" t="n"/>
@@ -726,607 +726,623 @@
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="n"/>
-      <c r="C11" s="19" t="n"/>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="19" t="n"/>
-      <c r="G11" s="19" t="n"/>
-      <c r="H11" s="19" t="n"/>
-      <c r="I11" s="19" t="n"/>
-      <c r="J11" s="19" t="n"/>
-      <c r="K11" s="19" t="n"/>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="n"/>
-      <c r="C13" s="19" t="n"/>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="19" t="n"/>
-      <c r="F13" s="19" t="n"/>
-      <c r="G13" s="19" t="n"/>
-      <c r="H13" s="19" t="n"/>
-      <c r="I13" s="19" t="n"/>
-      <c r="J13" s="19" t="n"/>
-      <c r="K13" s="19" t="n"/>
-    </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 355억      당일 2026-07-06  vs  전영업일 2026-07-03      매수 4종목  /  매도 3종목</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,420억      당일 2026-07-06  vs  전영업일 2026-07-03      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,814억      당일 2026-07-06  vs  전영업일 2026-07-03      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 366억      당일 2026-07-06  vs  전영업일 2026-07-03      매수 4종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>전체대비비중</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>전체대비비중</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>네패스아크  (신규)</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="C18" s="11" t="n">
-        <v>53676000</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>0→21</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>LS증권</t>
-        </is>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>-91</v>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v>-48412000</v>
-      </c>
-      <c r="J18" s="16" t="n">
-        <v>-0.136</v>
-      </c>
-      <c r="K18" s="13" t="inlineStr">
-        <is>
-          <t>376→285</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>티씨케이</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" s="11" t="n">
-        <v>60240000</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>44→47</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I19" s="15" t="n">
-        <v>-87936000</v>
-      </c>
-      <c r="J19" s="16" t="n">
-        <v>-0.248</v>
-      </c>
-      <c r="K19" s="13" t="inlineStr">
-        <is>
-          <t>210→186</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>네패스아크  (신규)</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>43920000</v>
+        <v>56868000</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.124</v>
+        <v>0.155</v>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>60→63</t>
+          <t>0→21</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>LS증권</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-13</v>
+        <v>-91</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-105040000</v>
+        <v>-49358400</v>
       </c>
       <c r="J20" s="16" t="n">
-        <v>-0.296</v>
+        <v>-0.135</v>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>98→85</t>
+          <t>376→285</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>42672000</v>
+        <v>58800000</v>
       </c>
       <c r="D21" s="12" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>44→47</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>-99456000</v>
+      </c>
+      <c r="J21" s="16" t="n">
+        <v>-0.272</v>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>210→186</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>42552000</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>72→75</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>두산테스나</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-111800000</v>
+      </c>
+      <c r="J22" s="16" t="n">
+        <v>-0.305</v>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>98→85</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>43752000</v>
+      </c>
+      <c r="D23" s="12" t="n">
         <v>0.12</v>
       </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>72→75</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="20" t="n"/>
-      <c r="I21" s="20" t="n"/>
-      <c r="J21" s="20" t="n"/>
-      <c r="K21" s="20" t="n"/>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>60→63</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 632억      당일 2026-07-06  vs  전영업일 2026-07-03      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>전체대비비중</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>전체대비비중</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>큐리오시스  (신규)</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="n">
-        <v>297</v>
-      </c>
-      <c r="C26" s="11" t="n">
-        <v>832312800</v>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>1.316</v>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>0→297</t>
-        </is>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>지아이이노베이션  (편출)</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>-685</v>
-      </c>
-      <c r="I26" s="15" t="n">
-        <v>-719866500</v>
-      </c>
-      <c r="J26" s="16" t="n">
-        <v>-1.138</v>
-      </c>
-      <c r="K26" s="13" t="inlineStr">
-        <is>
-          <t>685→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>리센스메디컬</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="n">
-        <v>77</v>
-      </c>
-      <c r="C27" s="11" t="n">
-        <v>146176800</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>530→607</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>올릭스</t>
-        </is>
-      </c>
-      <c r="H27" s="15" t="n">
-        <v>-122</v>
-      </c>
-      <c r="I27" s="15" t="n">
-        <v>-2058249800</v>
-      </c>
-      <c r="J27" s="16" t="n">
-        <v>-3.255</v>
-      </c>
-      <c r="K27" s="13" t="inlineStr">
-        <is>
-          <t>462→340</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>큐리오시스  (신규)</t>
         </is>
       </c>
       <c r="B28" s="11" t="n">
-        <v>35</v>
+        <v>297</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>726138000</v>
+        <v>854409600</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>1.148</v>
+        <v>1.352</v>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>152→187</t>
+          <t>0→297</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>지아이이노베이션  (편출)</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-36</v>
+        <v>-685</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-543891600</v>
+        <v>-738978000</v>
       </c>
       <c r="J28" s="16" t="n">
-        <v>-0.86</v>
+        <v>-1.169</v>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>395→359</t>
+          <t>685→0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>리센스메디컬</t>
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>834392000</v>
+        <v>150057600</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>1.319</v>
+        <v>0.237</v>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>59→75</t>
+          <t>530→607</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-13</v>
+        <v>-122</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-501663500</v>
+        <v>-2112893600</v>
       </c>
       <c r="J29" s="16" t="n">
-        <v>-0.793</v>
+        <v>-3.343</v>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>157→144</t>
+          <t>462→340</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B30" s="11" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>539462000</v>
+        <v>745416000</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>0.853</v>
+        <v>1.179</v>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>32→46</t>
-        </is>
-      </c>
-      <c r="G30" s="20" t="n"/>
-      <c r="H30" s="20" t="n"/>
-      <c r="I30" s="20" t="n"/>
-      <c r="J30" s="20" t="n"/>
-      <c r="K30" s="20" t="n"/>
+          <t>152→187</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>-36</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>-558331200</v>
+      </c>
+      <c r="J30" s="16" t="n">
+        <v>-0.883</v>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>395→359</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>856544000</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>59→75</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>-514982000</v>
+      </c>
+      <c r="J31" s="16" t="n">
+        <v>-0.8149999999999999</v>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>157→144</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>553784000</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>32→46</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="n"/>
+      <c r="H32" s="18" t="n"/>
+      <c r="I32" s="18" t="n"/>
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="18" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
           <t>에이비엘바이오</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n">
+      <c r="B33" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C31" s="11" t="n">
-        <v>43437200</v>
-      </c>
-      <c r="D31" s="12" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="C33" s="11" t="n">
+        <v>44590400</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>409→413</t>
         </is>
       </c>
-      <c r="G31" s="20" t="n"/>
-      <c r="H31" s="20" t="n"/>
-      <c r="I31" s="20" t="n"/>
-      <c r="J31" s="20" t="n"/>
-      <c r="K31" s="20" t="n"/>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="18" t="n"/>
+    </row>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n"/>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="19" t="n"/>
-      <c r="G33" s="19" t="n"/>
-      <c r="H33" s="19" t="n"/>
-      <c r="I33" s="19" t="n"/>
-      <c r="J33" s="19" t="n"/>
-      <c r="K33" s="19" t="n"/>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="20" t="n"/>
+      <c r="F35" s="20" t="n"/>
+      <c r="G35" s="20" t="n"/>
+      <c r="H35" s="20" t="n"/>
+      <c r="I35" s="20" t="n"/>
+      <c r="J35" s="20" t="n"/>
+      <c r="K35" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="G26:K26"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A35:K35"/>
     <mergeCell ref="A15:K15"/>
-    <mergeCell ref="G24:K24"/>
-    <mergeCell ref="G16:K16"/>
+    <mergeCell ref="A25:K25"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A14:K14"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A17:K17"/>
     <mergeCell ref="A9:K9"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="A8:K8"/>

--- a/reports/pdf_change_20260706.xlsx
+++ b/reports/pdf_change_20260706.xlsx
@@ -905,21 +905,21 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>58800000</v>
+        <v>42552000</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.161</v>
+        <v>0.116</v>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>44→47</t>
+          <t>72→75</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -945,21 +945,21 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>42552000</v>
+        <v>58800000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.116</v>
+        <v>0.161</v>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>72→75</t>
+          <t>44→47</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">

--- a/reports/pdf_change_20260706.xlsx
+++ b/reports/pdf_change_20260706.xlsx
@@ -905,21 +905,21 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>42552000</v>
+        <v>58800000</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.116</v>
+        <v>0.161</v>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>72→75</t>
+          <t>44→47</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -945,21 +945,21 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>58800000</v>
+        <v>43752000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.161</v>
+        <v>0.12</v>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>44→47</t>
+          <t>60→63</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -985,21 +985,21 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>43752000</v>
+        <v>42552000</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.12</v>
+        <v>0.116</v>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>60→63</t>
+          <t>72→75</t>
         </is>
       </c>
       <c r="G23" s="18" t="n"/>
